--- a/mod_project/data_tables/traps.xlsx
+++ b/mod_project/data_tables/traps.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Damage Floor (50% HP)</t>
+          <t>Damage Floor (25% HP)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mine (50% HP)</t>
+          <t>Mine (25% HP)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Killer Floor (50% KO | 100 Earth Res Null)</t>
+          <t>Killer Floor (25% KO | 100 Earth Res Null)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
